--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260814.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>5,759,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>5,759,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -660,29 +660,29 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.52%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>4,651,677,318</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -726,288 +726,288 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>20,089,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,089,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>35,274,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>35,274,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>11,165,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,165,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>3,346,403,838</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1100,29 +1100,29 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1166,46 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>2,634,625,322</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,154 +1217,154 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,660,185,322</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>23,751,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1408,68 +1408,68 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,22 +1481,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1562,24 +1562,24 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,66 +1591,66 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,22 +1701,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-15,613,268</t>
+          <t>-30,947,675</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
